--- a/TH1MKT.xlsx
+++ b/TH1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="50">
   <si>
     <t/>
   </si>
   <si>
-    <t>20002988</t>
-  </si>
-  <si>
-    <t>KUSUKA KRP AYM LD 60</t>
+    <t>20139550</t>
+  </si>
+  <si>
+    <t>REGEN LMN LIME 300ML</t>
   </si>
   <si>
     <t>TH1MKT</t>
@@ -28,127 +28,103 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20002989</t>
-  </si>
-  <si>
-    <t>KUSUKA KRP KJ.BKR 60</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20141124</t>
+  </si>
+  <si>
+    <t>REGEN ORANGE 300ML</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20091225</t>
-  </si>
-  <si>
-    <t>OVLTNE CHO BISC 104G</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10016646</t>
-  </si>
-  <si>
-    <t>INDO/F KECAP MN.R725</t>
-  </si>
-  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20136277</t>
-  </si>
-  <si>
-    <t>SNPRD FRT MG.PINE220</t>
-  </si>
-  <si>
-    <t>20120928</t>
-  </si>
-  <si>
-    <t>IM-BOOST VIT C&amp;D3 4S</t>
+    <t>20128233</t>
+  </si>
+  <si>
+    <t>NU CHO TEA HZLTEA330</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20137510</t>
-  </si>
-  <si>
-    <t>C/LANG KY PTH ROL 15</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20062306</t>
-  </si>
-  <si>
-    <t>RXONA MEN DEO ICE 45</t>
+    <t>20138202</t>
+  </si>
+  <si>
+    <t>NU MATCHA LATTEA 330</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20040383</t>
+  </si>
+  <si>
+    <t>NU MILK TEA 330ML</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20069527</t>
+  </si>
+  <si>
+    <t>NU TEH TARIK 330ML</t>
+  </si>
+  <si>
+    <t>20087713</t>
+  </si>
+  <si>
+    <t>IDM NDL AYM PDS 90G</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20129840</t>
+  </si>
+  <si>
+    <t>IDM MIE GRG INDO 88G</t>
+  </si>
+  <si>
+    <t>20129841</t>
+  </si>
+  <si>
+    <t>IDM MIE GRG PDS 92G</t>
+  </si>
+  <si>
+    <t>20091175</t>
+  </si>
+  <si>
+    <t>PEPSODNT KIDS STR 45</t>
   </si>
   <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20062307</t>
-  </si>
-  <si>
-    <t>RXONA MEN DEO INV 50</t>
-  </si>
-  <si>
-    <t>20062308</t>
-  </si>
-  <si>
-    <t>RXONA MEN DEO SPR 45</t>
-  </si>
-  <si>
-    <t>20062309</t>
-  </si>
-  <si>
-    <t>RXNA MEN DEO ULTR 45</t>
-  </si>
-  <si>
-    <t>20139354</t>
-  </si>
-  <si>
-    <t>RXONA MEN FR.STRK 40</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139522</t>
-  </si>
-  <si>
-    <t>RXONA MEN DRY DEF 40</t>
-  </si>
-  <si>
-    <t>10040202</t>
-  </si>
-  <si>
-    <t>SOFFELL A.NYMK K/J60</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20078241</t>
-  </si>
-  <si>
-    <t>SOFFELL LOT.APEL 60G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20128713</t>
-  </si>
-  <si>
-    <t>SOFEL LOT.KRN/SMR 60</t>
+    <t>10037208</t>
+  </si>
+  <si>
+    <t>CLOSE UP MT.FRSH 110</t>
+  </si>
+  <si>
+    <t>20027167</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP400</t>
+  </si>
+  <si>
+    <t>20104950</t>
+  </si>
+  <si>
+    <t>RINSO MLTO JP/PCH510</t>
+  </si>
+  <si>
+    <t>PT</t>
   </si>
   <si>
     <t>20054750</t>
@@ -157,21 +133,12 @@
     <t>RNSO+ML LIQ PRFM 510</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
     <t>20093188</t>
   </si>
   <si>
     <t>RINSO MLTO GLD LQ510</t>
   </si>
   <si>
-    <t>20104950</t>
-  </si>
-  <si>
-    <t>RINSO MLTO JP/PCH510</t>
-  </si>
-  <si>
     <t>20122879</t>
   </si>
   <si>
@@ -188,6 +155,12 @@
   </si>
   <si>
     <t>RINSO PURE LIQ 510G</t>
+  </si>
+  <si>
+    <t>20112492</t>
+  </si>
+  <si>
+    <t>SUNLIGHT JRK NPS400G</t>
   </si>
 </sst>
 </file>
@@ -580,14 +553,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -647,127 +620,127 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -781,13 +754,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -801,53 +774,53 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -861,193 +834,133 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
